--- a/artfynd/A 40056-2024 artfynd.xlsx
+++ b/artfynd/A 40056-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123408387</v>
+        <v>123408374</v>
       </c>
       <c r="B2" t="n">
-        <v>78769</v>
+        <v>57634</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741795</v>
+        <v>741856</v>
       </c>
       <c r="R2" t="n">
-        <v>7271067</v>
+        <v>7271107</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123408405</v>
+        <v>123408385</v>
       </c>
       <c r="B3" t="n">
-        <v>78153</v>
+        <v>78771</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741736</v>
+        <v>741865</v>
       </c>
       <c r="R3" t="n">
-        <v>7271115</v>
+        <v>7271092</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123408395</v>
+        <v>123408405</v>
       </c>
       <c r="B4" t="n">
-        <v>78769</v>
+        <v>78155</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741658</v>
+        <v>741736</v>
       </c>
       <c r="R4" t="n">
-        <v>7271147</v>
+        <v>7271115</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123408388</v>
+        <v>123408386</v>
       </c>
       <c r="B5" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741796</v>
+        <v>741856</v>
       </c>
       <c r="R5" t="n">
-        <v>7271062</v>
+        <v>7271107</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
         <v>123408384</v>
       </c>
       <c r="B6" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123408376</v>
+        <v>123408387</v>
       </c>
       <c r="B7" t="n">
-        <v>79879</v>
+        <v>78771</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741879</v>
+        <v>741795</v>
       </c>
       <c r="R7" t="n">
-        <v>7271009</v>
+        <v>7271067</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123408377</v>
+        <v>123408375</v>
       </c>
       <c r="B8" t="n">
-        <v>79879</v>
+        <v>79881</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741817</v>
+        <v>741891</v>
       </c>
       <c r="R8" t="n">
-        <v>7271078</v>
+        <v>7271047</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123408366</v>
+        <v>123408376</v>
       </c>
       <c r="B9" t="n">
-        <v>90920</v>
+        <v>79881</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741792</v>
+        <v>741879</v>
       </c>
       <c r="R9" t="n">
-        <v>7271089</v>
+        <v>7271009</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123408396</v>
+        <v>123408404</v>
       </c>
       <c r="B10" t="n">
-        <v>78769</v>
+        <v>78416</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741686</v>
+        <v>741781</v>
       </c>
       <c r="R10" t="n">
-        <v>7271160</v>
+        <v>7271097</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123408404</v>
+        <v>123408396</v>
       </c>
       <c r="B11" t="n">
-        <v>78414</v>
+        <v>78771</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741781</v>
+        <v>741686</v>
       </c>
       <c r="R11" t="n">
-        <v>7271097</v>
+        <v>7271160</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123408391</v>
+        <v>123408388</v>
       </c>
       <c r="B12" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741715</v>
+        <v>741796</v>
       </c>
       <c r="R12" t="n">
-        <v>7271135</v>
+        <v>7271062</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123408381</v>
+        <v>123408382</v>
       </c>
       <c r="B13" t="n">
         <v>57592</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741748</v>
+        <v>741744</v>
       </c>
       <c r="R13" t="n">
-        <v>7271084</v>
+        <v>7271111</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123408375</v>
+        <v>123408389</v>
       </c>
       <c r="B14" t="n">
-        <v>79879</v>
+        <v>78771</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741891</v>
+        <v>741751</v>
       </c>
       <c r="R14" t="n">
-        <v>7271047</v>
+        <v>7271065</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123408385</v>
+        <v>123408381</v>
       </c>
       <c r="B15" t="n">
-        <v>78769</v>
+        <v>57592</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741865</v>
+        <v>741748</v>
       </c>
       <c r="R15" t="n">
-        <v>7271092</v>
+        <v>7271084</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123408389</v>
+        <v>123408377</v>
       </c>
       <c r="B16" t="n">
-        <v>78769</v>
+        <v>79881</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741751</v>
+        <v>741817</v>
       </c>
       <c r="R16" t="n">
-        <v>7271065</v>
+        <v>7271078</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123408367</v>
+        <v>123408366</v>
       </c>
       <c r="B17" t="n">
-        <v>79358</v>
+        <v>90922</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741805</v>
+        <v>741792</v>
       </c>
       <c r="R17" t="n">
-        <v>7271057</v>
+        <v>7271089</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123408386</v>
+        <v>123408391</v>
       </c>
       <c r="B18" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741856</v>
+        <v>741715</v>
       </c>
       <c r="R18" t="n">
-        <v>7271107</v>
+        <v>7271135</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123408382</v>
+        <v>123408395</v>
       </c>
       <c r="B19" t="n">
-        <v>57592</v>
+        <v>78771</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,25 +2421,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741744</v>
+        <v>741658</v>
       </c>
       <c r="R19" t="n">
-        <v>7271111</v>
+        <v>7271147</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2514,7 +2514,7 @@
         <v>123408390</v>
       </c>
       <c r="B20" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123408374</v>
+        <v>123408367</v>
       </c>
       <c r="B21" t="n">
-        <v>57634</v>
+        <v>79360</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741856</v>
+        <v>741805</v>
       </c>
       <c r="R21" t="n">
-        <v>7271107</v>
+        <v>7271057</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 40056-2024 artfynd.xlsx
+++ b/artfynd/A 40056-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123408374</v>
+        <v>123408395</v>
       </c>
       <c r="B2" t="n">
-        <v>57634</v>
+        <v>78772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741856</v>
+        <v>741658</v>
       </c>
       <c r="R2" t="n">
-        <v>7271107</v>
+        <v>7271147</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123408385</v>
+        <v>123408375</v>
       </c>
       <c r="B3" t="n">
-        <v>78771</v>
+        <v>79882</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741865</v>
+        <v>741891</v>
       </c>
       <c r="R3" t="n">
-        <v>7271092</v>
+        <v>7271047</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123408405</v>
+        <v>123408386</v>
       </c>
       <c r="B4" t="n">
-        <v>78155</v>
+        <v>78772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741736</v>
+        <v>741856</v>
       </c>
       <c r="R4" t="n">
-        <v>7271115</v>
+        <v>7271107</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123408386</v>
+        <v>123408389</v>
       </c>
       <c r="B5" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741856</v>
+        <v>741751</v>
       </c>
       <c r="R5" t="n">
-        <v>7271107</v>
+        <v>7271065</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123408384</v>
+        <v>123408376</v>
       </c>
       <c r="B6" t="n">
-        <v>78771</v>
+        <v>79882</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>742058</v>
+        <v>741879</v>
       </c>
       <c r="R6" t="n">
-        <v>7271140</v>
+        <v>7271009</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123408387</v>
+        <v>123408366</v>
       </c>
       <c r="B7" t="n">
-        <v>78771</v>
+        <v>90928</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741795</v>
+        <v>741792</v>
       </c>
       <c r="R7" t="n">
-        <v>7271067</v>
+        <v>7271089</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123408375</v>
+        <v>123408381</v>
       </c>
       <c r="B8" t="n">
-        <v>79881</v>
+        <v>57592</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741891</v>
+        <v>741748</v>
       </c>
       <c r="R8" t="n">
-        <v>7271047</v>
+        <v>7271084</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123408376</v>
+        <v>123408396</v>
       </c>
       <c r="B9" t="n">
-        <v>79881</v>
+        <v>78772</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741879</v>
+        <v>741686</v>
       </c>
       <c r="R9" t="n">
-        <v>7271009</v>
+        <v>7271160</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123408404</v>
+        <v>123408374</v>
       </c>
       <c r="B10" t="n">
-        <v>78416</v>
+        <v>57634</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741781</v>
+        <v>741856</v>
       </c>
       <c r="R10" t="n">
-        <v>7271097</v>
+        <v>7271107</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123408396</v>
+        <v>123408388</v>
       </c>
       <c r="B11" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741686</v>
+        <v>741796</v>
       </c>
       <c r="R11" t="n">
-        <v>7271160</v>
+        <v>7271062</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123408388</v>
+        <v>123408387</v>
       </c>
       <c r="B12" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741796</v>
+        <v>741795</v>
       </c>
       <c r="R12" t="n">
-        <v>7271062</v>
+        <v>7271067</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123408382</v>
+        <v>123408404</v>
       </c>
       <c r="B13" t="n">
-        <v>57592</v>
+        <v>78417</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741744</v>
+        <v>741781</v>
       </c>
       <c r="R13" t="n">
-        <v>7271111</v>
+        <v>7271097</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123408389</v>
+        <v>123408382</v>
       </c>
       <c r="B14" t="n">
-        <v>78771</v>
+        <v>57592</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741751</v>
+        <v>741744</v>
       </c>
       <c r="R14" t="n">
-        <v>7271065</v>
+        <v>7271111</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123408381</v>
+        <v>123408385</v>
       </c>
       <c r="B15" t="n">
-        <v>57592</v>
+        <v>78772</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741748</v>
+        <v>741865</v>
       </c>
       <c r="R15" t="n">
-        <v>7271084</v>
+        <v>7271092</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2106,7 +2106,7 @@
         <v>123408377</v>
       </c>
       <c r="B16" t="n">
-        <v>79881</v>
+        <v>79882</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123408366</v>
+        <v>123408384</v>
       </c>
       <c r="B17" t="n">
-        <v>90922</v>
+        <v>78772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741792</v>
+        <v>742058</v>
       </c>
       <c r="R17" t="n">
-        <v>7271089</v>
+        <v>7271140</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123408391</v>
+        <v>123408405</v>
       </c>
       <c r="B18" t="n">
-        <v>78771</v>
+        <v>78156</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741715</v>
+        <v>741736</v>
       </c>
       <c r="R18" t="n">
-        <v>7271135</v>
+        <v>7271115</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123408395</v>
+        <v>123408390</v>
       </c>
       <c r="B19" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741658</v>
+        <v>741728</v>
       </c>
       <c r="R19" t="n">
-        <v>7271147</v>
+        <v>7271129</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123408390</v>
+        <v>123408367</v>
       </c>
       <c r="B20" t="n">
-        <v>78771</v>
+        <v>79361</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741728</v>
+        <v>741805</v>
       </c>
       <c r="R20" t="n">
-        <v>7271129</v>
+        <v>7271057</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123408367</v>
+        <v>123408391</v>
       </c>
       <c r="B21" t="n">
-        <v>79360</v>
+        <v>78772</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741805</v>
+        <v>741715</v>
       </c>
       <c r="R21" t="n">
-        <v>7271057</v>
+        <v>7271135</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 40056-2024 artfynd.xlsx
+++ b/artfynd/A 40056-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123408395</v>
       </c>
       <c r="B2" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123408375</v>
+        <v>123408404</v>
       </c>
       <c r="B3" t="n">
-        <v>79882</v>
+        <v>78420</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741891</v>
+        <v>741781</v>
       </c>
       <c r="R3" t="n">
-        <v>7271047</v>
+        <v>7271097</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123408386</v>
+        <v>123408367</v>
       </c>
       <c r="B4" t="n">
-        <v>78772</v>
+        <v>79364</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741856</v>
+        <v>741805</v>
       </c>
       <c r="R4" t="n">
-        <v>7271107</v>
+        <v>7271057</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123408389</v>
+        <v>123408391</v>
       </c>
       <c r="B5" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741751</v>
+        <v>741715</v>
       </c>
       <c r="R5" t="n">
-        <v>7271065</v>
+        <v>7271135</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123408376</v>
+        <v>123408388</v>
       </c>
       <c r="B6" t="n">
-        <v>79882</v>
+        <v>78775</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741879</v>
+        <v>741796</v>
       </c>
       <c r="R6" t="n">
-        <v>7271009</v>
+        <v>7271062</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123408366</v>
+        <v>123408396</v>
       </c>
       <c r="B7" t="n">
-        <v>90928</v>
+        <v>78775</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741792</v>
+        <v>741686</v>
       </c>
       <c r="R7" t="n">
-        <v>7271089</v>
+        <v>7271160</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123408381</v>
+        <v>123408405</v>
       </c>
       <c r="B8" t="n">
-        <v>57592</v>
+        <v>78159</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741748</v>
+        <v>741736</v>
       </c>
       <c r="R8" t="n">
-        <v>7271084</v>
+        <v>7271115</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123408396</v>
+        <v>123408382</v>
       </c>
       <c r="B9" t="n">
-        <v>78772</v>
+        <v>57592</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741686</v>
+        <v>741744</v>
       </c>
       <c r="R9" t="n">
-        <v>7271160</v>
+        <v>7271111</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123408374</v>
+        <v>123408389</v>
       </c>
       <c r="B10" t="n">
-        <v>57634</v>
+        <v>78775</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741856</v>
+        <v>741751</v>
       </c>
       <c r="R10" t="n">
-        <v>7271107</v>
+        <v>7271065</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123408388</v>
+        <v>123408387</v>
       </c>
       <c r="B11" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741796</v>
+        <v>741795</v>
       </c>
       <c r="R11" t="n">
-        <v>7271062</v>
+        <v>7271067</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123408387</v>
+        <v>123408386</v>
       </c>
       <c r="B12" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741795</v>
+        <v>741856</v>
       </c>
       <c r="R12" t="n">
-        <v>7271067</v>
+        <v>7271107</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123408404</v>
+        <v>123408375</v>
       </c>
       <c r="B13" t="n">
-        <v>78417</v>
+        <v>79885</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741781</v>
+        <v>741891</v>
       </c>
       <c r="R13" t="n">
-        <v>7271097</v>
+        <v>7271047</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123408382</v>
+        <v>123408384</v>
       </c>
       <c r="B14" t="n">
-        <v>57592</v>
+        <v>78775</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741744</v>
+        <v>742058</v>
       </c>
       <c r="R14" t="n">
-        <v>7271111</v>
+        <v>7271140</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123408385</v>
+        <v>123408377</v>
       </c>
       <c r="B15" t="n">
-        <v>78772</v>
+        <v>79885</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741865</v>
+        <v>741817</v>
       </c>
       <c r="R15" t="n">
-        <v>7271092</v>
+        <v>7271078</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123408377</v>
+        <v>123408381</v>
       </c>
       <c r="B16" t="n">
-        <v>79882</v>
+        <v>57592</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741817</v>
+        <v>741748</v>
       </c>
       <c r="R16" t="n">
-        <v>7271078</v>
+        <v>7271084</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123408384</v>
+        <v>123408374</v>
       </c>
       <c r="B17" t="n">
-        <v>78772</v>
+        <v>57634</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>742058</v>
+        <v>741856</v>
       </c>
       <c r="R17" t="n">
-        <v>7271140</v>
+        <v>7271107</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123408405</v>
+        <v>123408366</v>
       </c>
       <c r="B18" t="n">
-        <v>78156</v>
+        <v>90931</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2319,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741736</v>
+        <v>741792</v>
       </c>
       <c r="R18" t="n">
-        <v>7271115</v>
+        <v>7271089</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123408390</v>
+        <v>123408376</v>
       </c>
       <c r="B19" t="n">
-        <v>78772</v>
+        <v>79885</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,25 +2421,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741728</v>
+        <v>741879</v>
       </c>
       <c r="R19" t="n">
-        <v>7271129</v>
+        <v>7271009</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123408367</v>
+        <v>123408390</v>
       </c>
       <c r="B20" t="n">
-        <v>79361</v>
+        <v>78775</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741805</v>
+        <v>741728</v>
       </c>
       <c r="R20" t="n">
-        <v>7271057</v>
+        <v>7271129</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123408391</v>
+        <v>123408385</v>
       </c>
       <c r="B21" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741715</v>
+        <v>741865</v>
       </c>
       <c r="R21" t="n">
-        <v>7271135</v>
+        <v>7271092</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 40056-2024 artfynd.xlsx
+++ b/artfynd/A 40056-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123408395</v>
+        <v>123408404</v>
       </c>
       <c r="B2" t="n">
-        <v>78775</v>
+        <v>78426</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741658</v>
+        <v>741781</v>
       </c>
       <c r="R2" t="n">
-        <v>7271147</v>
+        <v>7271097</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123408404</v>
+        <v>123408405</v>
       </c>
       <c r="B3" t="n">
-        <v>78420</v>
+        <v>78165</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741781</v>
+        <v>741736</v>
       </c>
       <c r="R3" t="n">
-        <v>7271097</v>
+        <v>7271115</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123408367</v>
+        <v>123408382</v>
       </c>
       <c r="B4" t="n">
-        <v>79364</v>
+        <v>57598</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741805</v>
+        <v>741744</v>
       </c>
       <c r="R4" t="n">
-        <v>7271057</v>
+        <v>7271111</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123408391</v>
+        <v>123408387</v>
       </c>
       <c r="B5" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741715</v>
+        <v>741795</v>
       </c>
       <c r="R5" t="n">
-        <v>7271135</v>
+        <v>7271067</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123408388</v>
+        <v>123408386</v>
       </c>
       <c r="B6" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741796</v>
+        <v>741856</v>
       </c>
       <c r="R6" t="n">
-        <v>7271062</v>
+        <v>7271107</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123408396</v>
+        <v>123408390</v>
       </c>
       <c r="B7" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741686</v>
+        <v>741728</v>
       </c>
       <c r="R7" t="n">
-        <v>7271160</v>
+        <v>7271129</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123408405</v>
+        <v>123408385</v>
       </c>
       <c r="B8" t="n">
-        <v>78159</v>
+        <v>78781</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741736</v>
+        <v>741865</v>
       </c>
       <c r="R8" t="n">
-        <v>7271115</v>
+        <v>7271092</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123408382</v>
+        <v>123408366</v>
       </c>
       <c r="B9" t="n">
-        <v>57592</v>
+        <v>90948</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741744</v>
+        <v>741792</v>
       </c>
       <c r="R9" t="n">
-        <v>7271111</v>
+        <v>7271089</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123408389</v>
+        <v>123408391</v>
       </c>
       <c r="B10" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741751</v>
+        <v>741715</v>
       </c>
       <c r="R10" t="n">
-        <v>7271065</v>
+        <v>7271135</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123408387</v>
+        <v>123408388</v>
       </c>
       <c r="B11" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741795</v>
+        <v>741796</v>
       </c>
       <c r="R11" t="n">
-        <v>7271067</v>
+        <v>7271062</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123408386</v>
+        <v>123408395</v>
       </c>
       <c r="B12" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741856</v>
+        <v>741658</v>
       </c>
       <c r="R12" t="n">
-        <v>7271107</v>
+        <v>7271147</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123408375</v>
+        <v>123408374</v>
       </c>
       <c r="B13" t="n">
-        <v>79885</v>
+        <v>57640</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741891</v>
+        <v>741856</v>
       </c>
       <c r="R13" t="n">
-        <v>7271047</v>
+        <v>7271107</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123408384</v>
+        <v>123408376</v>
       </c>
       <c r="B14" t="n">
-        <v>78775</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>742058</v>
+        <v>741879</v>
       </c>
       <c r="R14" t="n">
-        <v>7271140</v>
+        <v>7271009</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123408377</v>
+        <v>123408396</v>
       </c>
       <c r="B15" t="n">
-        <v>79885</v>
+        <v>78781</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741817</v>
+        <v>741686</v>
       </c>
       <c r="R15" t="n">
-        <v>7271078</v>
+        <v>7271160</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123408381</v>
+        <v>123408377</v>
       </c>
       <c r="B16" t="n">
-        <v>57592</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741748</v>
+        <v>741817</v>
       </c>
       <c r="R16" t="n">
-        <v>7271084</v>
+        <v>7271078</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123408374</v>
+        <v>123408381</v>
       </c>
       <c r="B17" t="n">
-        <v>57634</v>
+        <v>57598</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741856</v>
+        <v>741748</v>
       </c>
       <c r="R17" t="n">
-        <v>7271107</v>
+        <v>7271084</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123408366</v>
+        <v>123408389</v>
       </c>
       <c r="B18" t="n">
-        <v>90931</v>
+        <v>78781</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2319,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741792</v>
+        <v>741751</v>
       </c>
       <c r="R18" t="n">
-        <v>7271089</v>
+        <v>7271065</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123408376</v>
+        <v>123408384</v>
       </c>
       <c r="B19" t="n">
-        <v>79885</v>
+        <v>78781</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,25 +2421,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741879</v>
+        <v>742058</v>
       </c>
       <c r="R19" t="n">
-        <v>7271009</v>
+        <v>7271140</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123408390</v>
+        <v>123408375</v>
       </c>
       <c r="B20" t="n">
-        <v>78775</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741728</v>
+        <v>741891</v>
       </c>
       <c r="R20" t="n">
-        <v>7271129</v>
+        <v>7271047</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123408385</v>
+        <v>123408367</v>
       </c>
       <c r="B21" t="n">
-        <v>78775</v>
+        <v>79370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741865</v>
+        <v>741805</v>
       </c>
       <c r="R21" t="n">
-        <v>7271092</v>
+        <v>7271057</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 40056-2024 artfynd.xlsx
+++ b/artfynd/A 40056-2024 artfynd.xlsx
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123408395</v>
+        <v>123408376</v>
       </c>
       <c r="B12" t="n">
-        <v>78781</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741658</v>
+        <v>741879</v>
       </c>
       <c r="R12" t="n">
-        <v>7271147</v>
+        <v>7271009</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123408374</v>
+        <v>123408395</v>
       </c>
       <c r="B13" t="n">
-        <v>57640</v>
+        <v>78781</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741856</v>
+        <v>741658</v>
       </c>
       <c r="R13" t="n">
-        <v>7271107</v>
+        <v>7271147</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123408376</v>
+        <v>123408374</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>57640</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741879</v>
+        <v>741856</v>
       </c>
       <c r="R14" t="n">
-        <v>7271009</v>
+        <v>7271107</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123408375</v>
+        <v>123408367</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>79370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741891</v>
+        <v>741805</v>
       </c>
       <c r="R20" t="n">
-        <v>7271047</v>
+        <v>7271057</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123408367</v>
+        <v>123408375</v>
       </c>
       <c r="B21" t="n">
-        <v>79370</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741805</v>
+        <v>741891</v>
       </c>
       <c r="R21" t="n">
-        <v>7271057</v>
+        <v>7271047</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 40056-2024 artfynd.xlsx
+++ b/artfynd/A 40056-2024 artfynd.xlsx
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123408376</v>
+        <v>123408395</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>78781</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741879</v>
+        <v>741658</v>
       </c>
       <c r="R12" t="n">
-        <v>7271009</v>
+        <v>7271147</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123408395</v>
+        <v>123408374</v>
       </c>
       <c r="B13" t="n">
-        <v>78781</v>
+        <v>57640</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741658</v>
+        <v>741856</v>
       </c>
       <c r="R13" t="n">
-        <v>7271147</v>
+        <v>7271107</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123408374</v>
+        <v>123408376</v>
       </c>
       <c r="B14" t="n">
-        <v>57640</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741856</v>
+        <v>741879</v>
       </c>
       <c r="R14" t="n">
-        <v>7271107</v>
+        <v>7271009</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 40056-2024 artfynd.xlsx
+++ b/artfynd/A 40056-2024 artfynd.xlsx
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123408367</v>
+        <v>123408375</v>
       </c>
       <c r="B20" t="n">
-        <v>79370</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741805</v>
+        <v>741891</v>
       </c>
       <c r="R20" t="n">
-        <v>7271057</v>
+        <v>7271047</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123408375</v>
+        <v>123408367</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>79370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741891</v>
+        <v>741805</v>
       </c>
       <c r="R21" t="n">
-        <v>7271047</v>
+        <v>7271057</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 40056-2024 artfynd.xlsx
+++ b/artfynd/A 40056-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123408404</v>
+        <v>123408391</v>
       </c>
       <c r="B2" t="n">
-        <v>78426</v>
+        <v>78786</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741781</v>
+        <v>741715</v>
       </c>
       <c r="R2" t="n">
-        <v>7271097</v>
+        <v>7271135</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123408405</v>
+        <v>123408387</v>
       </c>
       <c r="B3" t="n">
-        <v>78165</v>
+        <v>78786</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741736</v>
+        <v>741795</v>
       </c>
       <c r="R3" t="n">
-        <v>7271115</v>
+        <v>7271067</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123408382</v>
+        <v>123408375</v>
       </c>
       <c r="B4" t="n">
-        <v>57598</v>
+        <v>79896</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741744</v>
+        <v>741891</v>
       </c>
       <c r="R4" t="n">
-        <v>7271111</v>
+        <v>7271047</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123408387</v>
+        <v>123408377</v>
       </c>
       <c r="B5" t="n">
-        <v>78781</v>
+        <v>79896</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741795</v>
+        <v>741817</v>
       </c>
       <c r="R5" t="n">
-        <v>7271067</v>
+        <v>7271078</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123408386</v>
+        <v>123408390</v>
       </c>
       <c r="B6" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741856</v>
+        <v>741728</v>
       </c>
       <c r="R6" t="n">
-        <v>7271107</v>
+        <v>7271129</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123408390</v>
+        <v>123408376</v>
       </c>
       <c r="B7" t="n">
-        <v>78781</v>
+        <v>79896</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741728</v>
+        <v>741879</v>
       </c>
       <c r="R7" t="n">
-        <v>7271129</v>
+        <v>7271009</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123408385</v>
+        <v>123408367</v>
       </c>
       <c r="B8" t="n">
-        <v>78781</v>
+        <v>79375</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741865</v>
+        <v>741805</v>
       </c>
       <c r="R8" t="n">
-        <v>7271092</v>
+        <v>7271057</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123408366</v>
+        <v>123408386</v>
       </c>
       <c r="B9" t="n">
-        <v>90948</v>
+        <v>78786</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741792</v>
+        <v>741856</v>
       </c>
       <c r="R9" t="n">
-        <v>7271089</v>
+        <v>7271107</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123408391</v>
+        <v>123408404</v>
       </c>
       <c r="B10" t="n">
-        <v>78781</v>
+        <v>78431</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741715</v>
+        <v>741781</v>
       </c>
       <c r="R10" t="n">
-        <v>7271135</v>
+        <v>7271097</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123408388</v>
+        <v>123408366</v>
       </c>
       <c r="B11" t="n">
-        <v>78781</v>
+        <v>90953</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741796</v>
+        <v>741792</v>
       </c>
       <c r="R11" t="n">
-        <v>7271062</v>
+        <v>7271089</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123408395</v>
+        <v>123408388</v>
       </c>
       <c r="B12" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741658</v>
+        <v>741796</v>
       </c>
       <c r="R12" t="n">
-        <v>7271147</v>
+        <v>7271062</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123408374</v>
+        <v>123408385</v>
       </c>
       <c r="B13" t="n">
-        <v>57640</v>
+        <v>78786</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741856</v>
+        <v>741865</v>
       </c>
       <c r="R13" t="n">
-        <v>7271107</v>
+        <v>7271092</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123408376</v>
+        <v>123408405</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>78170</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741879</v>
+        <v>741736</v>
       </c>
       <c r="R14" t="n">
-        <v>7271009</v>
+        <v>7271115</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123408396</v>
+        <v>123408384</v>
       </c>
       <c r="B15" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741686</v>
+        <v>742058</v>
       </c>
       <c r="R15" t="n">
-        <v>7271160</v>
+        <v>7271140</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123408377</v>
+        <v>123408389</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>78786</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741817</v>
+        <v>741751</v>
       </c>
       <c r="R16" t="n">
-        <v>7271078</v>
+        <v>7271065</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123408381</v>
+        <v>123408395</v>
       </c>
       <c r="B17" t="n">
-        <v>57598</v>
+        <v>78786</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741748</v>
+        <v>741658</v>
       </c>
       <c r="R17" t="n">
-        <v>7271084</v>
+        <v>7271147</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123408389</v>
+        <v>123408381</v>
       </c>
       <c r="B18" t="n">
-        <v>78781</v>
+        <v>57601</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2319,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741751</v>
+        <v>741748</v>
       </c>
       <c r="R18" t="n">
-        <v>7271065</v>
+        <v>7271084</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123408384</v>
+        <v>123408396</v>
       </c>
       <c r="B19" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>742058</v>
+        <v>741686</v>
       </c>
       <c r="R19" t="n">
-        <v>7271140</v>
+        <v>7271160</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123408375</v>
+        <v>123408374</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>57643</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741891</v>
+        <v>741856</v>
       </c>
       <c r="R20" t="n">
-        <v>7271047</v>
+        <v>7271107</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123408367</v>
+        <v>123408382</v>
       </c>
       <c r="B21" t="n">
-        <v>79370</v>
+        <v>57601</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741805</v>
+        <v>741744</v>
       </c>
       <c r="R21" t="n">
-        <v>7271057</v>
+        <v>7271111</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 40056-2024 artfynd.xlsx
+++ b/artfynd/A 40056-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123408391</v>
+        <v>123408389</v>
       </c>
       <c r="B2" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741715</v>
+        <v>741751</v>
       </c>
       <c r="R2" t="n">
-        <v>7271135</v>
+        <v>7271065</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123408387</v>
+        <v>123408405</v>
       </c>
       <c r="B3" t="n">
-        <v>78786</v>
+        <v>78172</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741795</v>
+        <v>741736</v>
       </c>
       <c r="R3" t="n">
-        <v>7271067</v>
+        <v>7271115</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123408375</v>
+        <v>123408386</v>
       </c>
       <c r="B4" t="n">
-        <v>79896</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741891</v>
+        <v>741856</v>
       </c>
       <c r="R4" t="n">
-        <v>7271047</v>
+        <v>7271107</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123408377</v>
+        <v>123408385</v>
       </c>
       <c r="B5" t="n">
-        <v>79896</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741817</v>
+        <v>741865</v>
       </c>
       <c r="R5" t="n">
-        <v>7271078</v>
+        <v>7271092</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123408390</v>
+        <v>123408396</v>
       </c>
       <c r="B6" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741728</v>
+        <v>741686</v>
       </c>
       <c r="R6" t="n">
-        <v>7271129</v>
+        <v>7271160</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123408376</v>
+        <v>123408391</v>
       </c>
       <c r="B7" t="n">
-        <v>79896</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741879</v>
+        <v>741715</v>
       </c>
       <c r="R7" t="n">
-        <v>7271009</v>
+        <v>7271135</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123408367</v>
+        <v>123408366</v>
       </c>
       <c r="B8" t="n">
-        <v>79375</v>
+        <v>90955</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741805</v>
+        <v>741792</v>
       </c>
       <c r="R8" t="n">
-        <v>7271057</v>
+        <v>7271089</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123408386</v>
+        <v>123408382</v>
       </c>
       <c r="B9" t="n">
-        <v>78786</v>
+        <v>57602</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741856</v>
+        <v>741744</v>
       </c>
       <c r="R9" t="n">
-        <v>7271107</v>
+        <v>7271111</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123408404</v>
+        <v>123408381</v>
       </c>
       <c r="B10" t="n">
-        <v>78431</v>
+        <v>57602</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741781</v>
+        <v>741748</v>
       </c>
       <c r="R10" t="n">
-        <v>7271097</v>
+        <v>7271084</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123408366</v>
+        <v>123408404</v>
       </c>
       <c r="B11" t="n">
-        <v>90953</v>
+        <v>78433</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741792</v>
+        <v>741781</v>
       </c>
       <c r="R11" t="n">
-        <v>7271089</v>
+        <v>7271097</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1698,7 @@
         <v>123408388</v>
       </c>
       <c r="B12" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123408385</v>
+        <v>123408377</v>
       </c>
       <c r="B13" t="n">
-        <v>78786</v>
+        <v>79898</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741865</v>
+        <v>741817</v>
       </c>
       <c r="R13" t="n">
-        <v>7271092</v>
+        <v>7271078</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123408405</v>
+        <v>123408375</v>
       </c>
       <c r="B14" t="n">
-        <v>78170</v>
+        <v>79898</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741736</v>
+        <v>741891</v>
       </c>
       <c r="R14" t="n">
-        <v>7271115</v>
+        <v>7271047</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123408384</v>
+        <v>123408387</v>
       </c>
       <c r="B15" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>742058</v>
+        <v>741795</v>
       </c>
       <c r="R15" t="n">
-        <v>7271140</v>
+        <v>7271067</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123408389</v>
+        <v>123408374</v>
       </c>
       <c r="B16" t="n">
-        <v>78786</v>
+        <v>57644</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741751</v>
+        <v>741856</v>
       </c>
       <c r="R16" t="n">
-        <v>7271065</v>
+        <v>7271107</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123408395</v>
+        <v>123408367</v>
       </c>
       <c r="B17" t="n">
-        <v>78786</v>
+        <v>79377</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741658</v>
+        <v>741805</v>
       </c>
       <c r="R17" t="n">
-        <v>7271147</v>
+        <v>7271057</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123408381</v>
+        <v>123408384</v>
       </c>
       <c r="B18" t="n">
-        <v>57601</v>
+        <v>78788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,25 +2319,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741748</v>
+        <v>742058</v>
       </c>
       <c r="R18" t="n">
-        <v>7271084</v>
+        <v>7271140</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123408396</v>
+        <v>123408395</v>
       </c>
       <c r="B19" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741686</v>
+        <v>741658</v>
       </c>
       <c r="R19" t="n">
-        <v>7271160</v>
+        <v>7271147</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123408374</v>
+        <v>123408376</v>
       </c>
       <c r="B20" t="n">
-        <v>57643</v>
+        <v>79898</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741856</v>
+        <v>741879</v>
       </c>
       <c r="R20" t="n">
-        <v>7271107</v>
+        <v>7271009</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123408382</v>
+        <v>123408390</v>
       </c>
       <c r="B21" t="n">
-        <v>57601</v>
+        <v>78788</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741744</v>
+        <v>741728</v>
       </c>
       <c r="R21" t="n">
-        <v>7271111</v>
+        <v>7271129</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 40056-2024 artfynd.xlsx
+++ b/artfynd/A 40056-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123408389</v>
+        <v>123408374</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>57644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741751</v>
+        <v>741856</v>
       </c>
       <c r="R2" t="n">
-        <v>7271065</v>
+        <v>7271107</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123408405</v>
+        <v>123408390</v>
       </c>
       <c r="B3" t="n">
-        <v>78172</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741736</v>
+        <v>741728</v>
       </c>
       <c r="R3" t="n">
-        <v>7271115</v>
+        <v>7271129</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123408386</v>
+        <v>123408382</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>57602</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741856</v>
+        <v>741744</v>
       </c>
       <c r="R4" t="n">
-        <v>7271107</v>
+        <v>7271111</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123408385</v>
+        <v>123408375</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741865</v>
+        <v>741891</v>
       </c>
       <c r="R5" t="n">
-        <v>7271092</v>
+        <v>7271047</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123408396</v>
+        <v>123408384</v>
       </c>
       <c r="B6" t="n">
         <v>78788</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741686</v>
+        <v>742058</v>
       </c>
       <c r="R6" t="n">
-        <v>7271160</v>
+        <v>7271140</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123408391</v>
+        <v>123408367</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741715</v>
+        <v>741805</v>
       </c>
       <c r="R7" t="n">
-        <v>7271135</v>
+        <v>7271057</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123408366</v>
+        <v>123408388</v>
       </c>
       <c r="B8" t="n">
-        <v>90955</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741792</v>
+        <v>741796</v>
       </c>
       <c r="R8" t="n">
-        <v>7271089</v>
+        <v>7271062</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123408382</v>
+        <v>123408389</v>
       </c>
       <c r="B9" t="n">
-        <v>57602</v>
+        <v>78788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741744</v>
+        <v>741751</v>
       </c>
       <c r="R9" t="n">
-        <v>7271111</v>
+        <v>7271065</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123408381</v>
+        <v>123408396</v>
       </c>
       <c r="B10" t="n">
-        <v>57602</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741748</v>
+        <v>741686</v>
       </c>
       <c r="R10" t="n">
-        <v>7271084</v>
+        <v>7271160</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123408404</v>
+        <v>123408385</v>
       </c>
       <c r="B11" t="n">
-        <v>78433</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741781</v>
+        <v>741865</v>
       </c>
       <c r="R11" t="n">
-        <v>7271097</v>
+        <v>7271092</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123408388</v>
+        <v>123408404</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>78433</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741796</v>
+        <v>741781</v>
       </c>
       <c r="R12" t="n">
-        <v>7271062</v>
+        <v>7271097</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123408377</v>
+        <v>123408391</v>
       </c>
       <c r="B13" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741817</v>
+        <v>741715</v>
       </c>
       <c r="R13" t="n">
-        <v>7271078</v>
+        <v>7271135</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123408375</v>
+        <v>123408381</v>
       </c>
       <c r="B14" t="n">
-        <v>79898</v>
+        <v>57602</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>103031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741891</v>
+        <v>741748</v>
       </c>
       <c r="R14" t="n">
-        <v>7271047</v>
+        <v>7271084</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123408387</v>
+        <v>123408386</v>
       </c>
       <c r="B15" t="n">
         <v>78788</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741795</v>
+        <v>741856</v>
       </c>
       <c r="R15" t="n">
-        <v>7271067</v>
+        <v>7271107</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123408374</v>
+        <v>123408395</v>
       </c>
       <c r="B16" t="n">
-        <v>57644</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741856</v>
+        <v>741658</v>
       </c>
       <c r="R16" t="n">
-        <v>7271107</v>
+        <v>7271147</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123408367</v>
+        <v>123408376</v>
       </c>
       <c r="B17" t="n">
-        <v>79377</v>
+        <v>79898</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741805</v>
+        <v>741879</v>
       </c>
       <c r="R17" t="n">
-        <v>7271057</v>
+        <v>7271009</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123408384</v>
+        <v>123408387</v>
       </c>
       <c r="B18" t="n">
         <v>78788</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>742058</v>
+        <v>741795</v>
       </c>
       <c r="R18" t="n">
-        <v>7271140</v>
+        <v>7271067</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123408395</v>
+        <v>123408366</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>90955</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,25 +2421,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741658</v>
+        <v>741792</v>
       </c>
       <c r="R19" t="n">
-        <v>7271147</v>
+        <v>7271089</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123408376</v>
+        <v>123408377</v>
       </c>
       <c r="B20" t="n">
         <v>79898</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741879</v>
+        <v>741817</v>
       </c>
       <c r="R20" t="n">
-        <v>7271009</v>
+        <v>7271078</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123408390</v>
+        <v>123408405</v>
       </c>
       <c r="B21" t="n">
-        <v>78788</v>
+        <v>78172</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741728</v>
+        <v>741736</v>
       </c>
       <c r="R21" t="n">
-        <v>7271129</v>
+        <v>7271115</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 40056-2024 artfynd.xlsx
+++ b/artfynd/A 40056-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123408374</v>
+        <v>123408377</v>
       </c>
       <c r="B2" t="n">
-        <v>57644</v>
+        <v>79898</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741856</v>
+        <v>741817</v>
       </c>
       <c r="R2" t="n">
-        <v>7271107</v>
+        <v>7271078</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123408390</v>
+        <v>123408387</v>
       </c>
       <c r="B3" t="n">
         <v>78788</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741728</v>
+        <v>741795</v>
       </c>
       <c r="R3" t="n">
-        <v>7271129</v>
+        <v>7271067</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123408382</v>
+        <v>123408386</v>
       </c>
       <c r="B4" t="n">
-        <v>57602</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741744</v>
+        <v>741856</v>
       </c>
       <c r="R4" t="n">
-        <v>7271111</v>
+        <v>7271107</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123408375</v>
+        <v>123408391</v>
       </c>
       <c r="B5" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741891</v>
+        <v>741715</v>
       </c>
       <c r="R5" t="n">
-        <v>7271047</v>
+        <v>7271135</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123408384</v>
+        <v>123408375</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>742058</v>
+        <v>741891</v>
       </c>
       <c r="R6" t="n">
-        <v>7271140</v>
+        <v>7271047</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123408367</v>
+        <v>123408405</v>
       </c>
       <c r="B7" t="n">
-        <v>79377</v>
+        <v>78172</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741805</v>
+        <v>741736</v>
       </c>
       <c r="R7" t="n">
-        <v>7271057</v>
+        <v>7271115</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123408388</v>
+        <v>123408367</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741796</v>
+        <v>741805</v>
       </c>
       <c r="R8" t="n">
-        <v>7271062</v>
+        <v>7271057</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123408389</v>
+        <v>123408384</v>
       </c>
       <c r="B9" t="n">
         <v>78788</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741751</v>
+        <v>742058</v>
       </c>
       <c r="R9" t="n">
-        <v>7271065</v>
+        <v>7271140</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123408396</v>
+        <v>123408374</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>57644</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741686</v>
+        <v>741856</v>
       </c>
       <c r="R10" t="n">
-        <v>7271160</v>
+        <v>7271107</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123408385</v>
+        <v>123408382</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>57602</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741865</v>
+        <v>741744</v>
       </c>
       <c r="R11" t="n">
-        <v>7271092</v>
+        <v>7271111</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123408404</v>
+        <v>123408396</v>
       </c>
       <c r="B12" t="n">
-        <v>78433</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741781</v>
+        <v>741686</v>
       </c>
       <c r="R12" t="n">
-        <v>7271097</v>
+        <v>7271160</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123408391</v>
+        <v>123408385</v>
       </c>
       <c r="B13" t="n">
         <v>78788</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741715</v>
+        <v>741865</v>
       </c>
       <c r="R13" t="n">
-        <v>7271135</v>
+        <v>7271092</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123408381</v>
+        <v>123408389</v>
       </c>
       <c r="B14" t="n">
-        <v>57602</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741748</v>
+        <v>741751</v>
       </c>
       <c r="R14" t="n">
-        <v>7271084</v>
+        <v>7271065</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123408386</v>
+        <v>123408381</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>57602</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741856</v>
+        <v>741748</v>
       </c>
       <c r="R15" t="n">
-        <v>7271107</v>
+        <v>7271084</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123408395</v>
+        <v>123408404</v>
       </c>
       <c r="B16" t="n">
-        <v>78788</v>
+        <v>78433</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741658</v>
+        <v>741781</v>
       </c>
       <c r="R16" t="n">
-        <v>7271147</v>
+        <v>7271097</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123408376</v>
+        <v>123408388</v>
       </c>
       <c r="B17" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741879</v>
+        <v>741796</v>
       </c>
       <c r="R17" t="n">
-        <v>7271009</v>
+        <v>7271062</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123408387</v>
+        <v>123408395</v>
       </c>
       <c r="B18" t="n">
         <v>78788</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741795</v>
+        <v>741658</v>
       </c>
       <c r="R18" t="n">
-        <v>7271067</v>
+        <v>7271147</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123408377</v>
+        <v>123408390</v>
       </c>
       <c r="B20" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741817</v>
+        <v>741728</v>
       </c>
       <c r="R20" t="n">
-        <v>7271078</v>
+        <v>7271129</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123408405</v>
+        <v>123408376</v>
       </c>
       <c r="B21" t="n">
-        <v>78172</v>
+        <v>79898</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741736</v>
+        <v>741879</v>
       </c>
       <c r="R21" t="n">
-        <v>7271115</v>
+        <v>7271009</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 40056-2024 artfynd.xlsx
+++ b/artfynd/A 40056-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123408387</v>
+        <v>123408405</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>78172</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741795</v>
+        <v>741736</v>
       </c>
       <c r="R3" t="n">
-        <v>7271067</v>
+        <v>7271115</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123408386</v>
+        <v>123408390</v>
       </c>
       <c r="B4" t="n">
         <v>78788</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741856</v>
+        <v>741728</v>
       </c>
       <c r="R4" t="n">
-        <v>7271107</v>
+        <v>7271129</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123408391</v>
+        <v>123408404</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>78433</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741715</v>
+        <v>741781</v>
       </c>
       <c r="R5" t="n">
-        <v>7271135</v>
+        <v>7271097</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123408375</v>
+        <v>123408366</v>
       </c>
       <c r="B6" t="n">
-        <v>79898</v>
+        <v>90955</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741891</v>
+        <v>741792</v>
       </c>
       <c r="R6" t="n">
-        <v>7271047</v>
+        <v>7271089</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123408405</v>
+        <v>123408384</v>
       </c>
       <c r="B7" t="n">
-        <v>78172</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741736</v>
+        <v>742058</v>
       </c>
       <c r="R7" t="n">
-        <v>7271115</v>
+        <v>7271140</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123408367</v>
+        <v>123408375</v>
       </c>
       <c r="B8" t="n">
-        <v>79377</v>
+        <v>79898</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741805</v>
+        <v>741891</v>
       </c>
       <c r="R8" t="n">
-        <v>7271057</v>
+        <v>7271047</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123408384</v>
+        <v>123408387</v>
       </c>
       <c r="B9" t="n">
         <v>78788</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>742058</v>
+        <v>741795</v>
       </c>
       <c r="R9" t="n">
-        <v>7271140</v>
+        <v>7271067</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123408374</v>
+        <v>123408396</v>
       </c>
       <c r="B10" t="n">
-        <v>57644</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741856</v>
+        <v>741686</v>
       </c>
       <c r="R10" t="n">
-        <v>7271107</v>
+        <v>7271160</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123408382</v>
+        <v>123408376</v>
       </c>
       <c r="B11" t="n">
-        <v>57602</v>
+        <v>79898</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103031</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741744</v>
+        <v>741879</v>
       </c>
       <c r="R11" t="n">
-        <v>7271111</v>
+        <v>7271009</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123408396</v>
+        <v>123408385</v>
       </c>
       <c r="B12" t="n">
         <v>78788</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741686</v>
+        <v>741865</v>
       </c>
       <c r="R12" t="n">
-        <v>7271160</v>
+        <v>7271092</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123408385</v>
+        <v>123408381</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>57602</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741865</v>
+        <v>741748</v>
       </c>
       <c r="R13" t="n">
-        <v>7271092</v>
+        <v>7271084</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123408389</v>
+        <v>123408386</v>
       </c>
       <c r="B14" t="n">
         <v>78788</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741751</v>
+        <v>741856</v>
       </c>
       <c r="R14" t="n">
-        <v>7271065</v>
+        <v>7271107</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123408381</v>
+        <v>123408374</v>
       </c>
       <c r="B15" t="n">
-        <v>57602</v>
+        <v>57644</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741748</v>
+        <v>741856</v>
       </c>
       <c r="R15" t="n">
-        <v>7271084</v>
+        <v>7271107</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123408404</v>
+        <v>123408391</v>
       </c>
       <c r="B16" t="n">
-        <v>78433</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741781</v>
+        <v>741715</v>
       </c>
       <c r="R16" t="n">
-        <v>7271097</v>
+        <v>7271135</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123408388</v>
+        <v>123408367</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741796</v>
+        <v>741805</v>
       </c>
       <c r="R17" t="n">
-        <v>7271062</v>
+        <v>7271057</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123408395</v>
+        <v>123408389</v>
       </c>
       <c r="B18" t="n">
         <v>78788</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741658</v>
+        <v>741751</v>
       </c>
       <c r="R18" t="n">
-        <v>7271147</v>
+        <v>7271065</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123408366</v>
+        <v>123408395</v>
       </c>
       <c r="B19" t="n">
-        <v>90955</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,25 +2421,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741792</v>
+        <v>741658</v>
       </c>
       <c r="R19" t="n">
-        <v>7271089</v>
+        <v>7271147</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123408390</v>
+        <v>123408382</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>57602</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741728</v>
+        <v>741744</v>
       </c>
       <c r="R20" t="n">
-        <v>7271129</v>
+        <v>7271111</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123408376</v>
+        <v>123408388</v>
       </c>
       <c r="B21" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741879</v>
+        <v>741796</v>
       </c>
       <c r="R21" t="n">
-        <v>7271009</v>
+        <v>7271062</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 40056-2024 artfynd.xlsx
+++ b/artfynd/A 40056-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123408377</v>
+        <v>123408366</v>
       </c>
       <c r="B2" t="n">
-        <v>79898</v>
+        <v>90955</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741817</v>
+        <v>741792</v>
       </c>
       <c r="R2" t="n">
-        <v>7271078</v>
+        <v>7271089</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123408390</v>
+        <v>123408385</v>
       </c>
       <c r="B4" t="n">
         <v>78788</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741728</v>
+        <v>741865</v>
       </c>
       <c r="R4" t="n">
-        <v>7271129</v>
+        <v>7271092</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123408404</v>
+        <v>123408381</v>
       </c>
       <c r="B5" t="n">
-        <v>78433</v>
+        <v>57602</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741781</v>
+        <v>741748</v>
       </c>
       <c r="R5" t="n">
-        <v>7271097</v>
+        <v>7271084</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123408366</v>
+        <v>123408384</v>
       </c>
       <c r="B6" t="n">
-        <v>90955</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>741792</v>
+        <v>742058</v>
       </c>
       <c r="R6" t="n">
-        <v>7271089</v>
+        <v>7271140</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123408384</v>
+        <v>123408374</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>57644</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>742058</v>
+        <v>741856</v>
       </c>
       <c r="R7" t="n">
-        <v>7271140</v>
+        <v>7271107</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123408375</v>
+        <v>123408367</v>
       </c>
       <c r="B8" t="n">
-        <v>79898</v>
+        <v>79377</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741891</v>
+        <v>741805</v>
       </c>
       <c r="R8" t="n">
-        <v>7271047</v>
+        <v>7271057</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123408387</v>
+        <v>123408391</v>
       </c>
       <c r="B9" t="n">
         <v>78788</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741795</v>
+        <v>741715</v>
       </c>
       <c r="R9" t="n">
-        <v>7271067</v>
+        <v>7271135</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123408396</v>
+        <v>123408376</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741686</v>
+        <v>741879</v>
       </c>
       <c r="R10" t="n">
-        <v>7271160</v>
+        <v>7271009</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123408376</v>
+        <v>123408382</v>
       </c>
       <c r="B11" t="n">
-        <v>79898</v>
+        <v>57602</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>103031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741879</v>
+        <v>741744</v>
       </c>
       <c r="R11" t="n">
-        <v>7271009</v>
+        <v>7271111</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123408385</v>
+        <v>123408395</v>
       </c>
       <c r="B12" t="n">
         <v>78788</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741865</v>
+        <v>741658</v>
       </c>
       <c r="R12" t="n">
-        <v>7271092</v>
+        <v>7271147</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123408381</v>
+        <v>123408375</v>
       </c>
       <c r="B13" t="n">
-        <v>57602</v>
+        <v>79898</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741748</v>
+        <v>741891</v>
       </c>
       <c r="R13" t="n">
-        <v>7271084</v>
+        <v>7271047</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123408386</v>
+        <v>123408404</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>78433</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741856</v>
+        <v>741781</v>
       </c>
       <c r="R14" t="n">
-        <v>7271107</v>
+        <v>7271097</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123408374</v>
+        <v>123408386</v>
       </c>
       <c r="B15" t="n">
-        <v>57644</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123408391</v>
+        <v>123408396</v>
       </c>
       <c r="B16" t="n">
         <v>78788</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741715</v>
+        <v>741686</v>
       </c>
       <c r="R16" t="n">
-        <v>7271135</v>
+        <v>7271160</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123408367</v>
+        <v>123408377</v>
       </c>
       <c r="B17" t="n">
-        <v>79377</v>
+        <v>79898</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741805</v>
+        <v>741817</v>
       </c>
       <c r="R17" t="n">
-        <v>7271057</v>
+        <v>7271078</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123408389</v>
+        <v>123408388</v>
       </c>
       <c r="B18" t="n">
         <v>78788</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>741751</v>
+        <v>741796</v>
       </c>
       <c r="R18" t="n">
-        <v>7271065</v>
+        <v>7271062</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123408395</v>
+        <v>123408389</v>
       </c>
       <c r="B19" t="n">
         <v>78788</v>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741658</v>
+        <v>741751</v>
       </c>
       <c r="R19" t="n">
-        <v>7271147</v>
+        <v>7271065</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123408382</v>
+        <v>123408390</v>
       </c>
       <c r="B20" t="n">
-        <v>57602</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2523,25 +2523,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741744</v>
+        <v>741728</v>
       </c>
       <c r="R20" t="n">
-        <v>7271111</v>
+        <v>7271129</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123408388</v>
+        <v>123408387</v>
       </c>
       <c r="B21" t="n">
         <v>78788</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741796</v>
+        <v>741795</v>
       </c>
       <c r="R21" t="n">
-        <v>7271062</v>
+        <v>7271067</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 40056-2024 artfynd.xlsx
+++ b/artfynd/A 40056-2024 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123408384</v>
+        <v>123408374</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>57644</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>742058</v>
+        <v>741856</v>
       </c>
       <c r="R6" t="n">
-        <v>7271140</v>
+        <v>7271107</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123408374</v>
+        <v>123408384</v>
       </c>
       <c r="B7" t="n">
-        <v>57644</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>741856</v>
+        <v>742058</v>
       </c>
       <c r="R7" t="n">
-        <v>7271107</v>
+        <v>7271140</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 40056-2024 artfynd.xlsx
+++ b/artfynd/A 40056-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123408366</v>
+        <v>123408387</v>
       </c>
       <c r="B2" t="n">
-        <v>90955</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>741792</v>
+        <v>741795</v>
       </c>
       <c r="R2" t="n">
-        <v>7271089</v>
+        <v>7271067</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123408405</v>
+        <v>123408366</v>
       </c>
       <c r="B3" t="n">
-        <v>78172</v>
+        <v>90955</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>741736</v>
+        <v>741792</v>
       </c>
       <c r="R3" t="n">
-        <v>7271115</v>
+        <v>7271089</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123408385</v>
+        <v>123408381</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>57602</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>741865</v>
+        <v>741748</v>
       </c>
       <c r="R4" t="n">
-        <v>7271092</v>
+        <v>7271084</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123408381</v>
+        <v>123408404</v>
       </c>
       <c r="B5" t="n">
-        <v>57602</v>
+        <v>78433</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>741748</v>
+        <v>741781</v>
       </c>
       <c r="R5" t="n">
-        <v>7271084</v>
+        <v>7271097</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123408374</v>
+        <v>123408386</v>
       </c>
       <c r="B6" t="n">
-        <v>57644</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123408384</v>
+        <v>123408391</v>
       </c>
       <c r="B7" t="n">
         <v>78788</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>742058</v>
+        <v>741715</v>
       </c>
       <c r="R7" t="n">
-        <v>7271140</v>
+        <v>7271135</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123408367</v>
+        <v>123408376</v>
       </c>
       <c r="B8" t="n">
-        <v>79377</v>
+        <v>79898</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>741805</v>
+        <v>741879</v>
       </c>
       <c r="R8" t="n">
-        <v>7271057</v>
+        <v>7271009</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123408391</v>
+        <v>123408367</v>
       </c>
       <c r="B9" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>741715</v>
+        <v>741805</v>
       </c>
       <c r="R9" t="n">
-        <v>7271135</v>
+        <v>7271057</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123408376</v>
+        <v>123408374</v>
       </c>
       <c r="B10" t="n">
-        <v>79898</v>
+        <v>57644</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>741879</v>
+        <v>741856</v>
       </c>
       <c r="R10" t="n">
-        <v>7271009</v>
+        <v>7271107</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123408382</v>
+        <v>123408389</v>
       </c>
       <c r="B11" t="n">
-        <v>57602</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>741744</v>
+        <v>741751</v>
       </c>
       <c r="R11" t="n">
-        <v>7271111</v>
+        <v>7271065</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123408395</v>
+        <v>123408385</v>
       </c>
       <c r="B12" t="n">
         <v>78788</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>741658</v>
+        <v>741865</v>
       </c>
       <c r="R12" t="n">
-        <v>7271147</v>
+        <v>7271092</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123408375</v>
+        <v>123408396</v>
       </c>
       <c r="B13" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>741891</v>
+        <v>741686</v>
       </c>
       <c r="R13" t="n">
-        <v>7271047</v>
+        <v>7271160</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123408404</v>
+        <v>123408395</v>
       </c>
       <c r="B14" t="n">
-        <v>78433</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>741781</v>
+        <v>741658</v>
       </c>
       <c r="R14" t="n">
-        <v>7271097</v>
+        <v>7271147</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123408386</v>
+        <v>123408405</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>78172</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>741856</v>
+        <v>741736</v>
       </c>
       <c r="R15" t="n">
-        <v>7271107</v>
+        <v>7271115</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123408396</v>
+        <v>123408377</v>
       </c>
       <c r="B16" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>741686</v>
+        <v>741817</v>
       </c>
       <c r="R16" t="n">
-        <v>7271160</v>
+        <v>7271078</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123408377</v>
+        <v>123408390</v>
       </c>
       <c r="B17" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2217,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>741817</v>
+        <v>741728</v>
       </c>
       <c r="R17" t="n">
-        <v>7271078</v>
+        <v>7271129</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123408389</v>
+        <v>123408375</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,25 +2421,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>741751</v>
+        <v>741891</v>
       </c>
       <c r="R19" t="n">
-        <v>7271065</v>
+        <v>7271047</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123408390</v>
+        <v>123408384</v>
       </c>
       <c r="B20" t="n">
         <v>78788</v>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>741728</v>
+        <v>742058</v>
       </c>
       <c r="R20" t="n">
-        <v>7271129</v>
+        <v>7271140</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123408387</v>
+        <v>123408382</v>
       </c>
       <c r="B21" t="n">
-        <v>78788</v>
+        <v>57602</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>741795</v>
+        <v>741744</v>
       </c>
       <c r="R21" t="n">
-        <v>7271067</v>
+        <v>7271111</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 40056-2024 artfynd.xlsx
+++ b/artfynd/A 40056-2024 artfynd.xlsx
@@ -2208,12 +2208,7 @@
         <v>123408382</v>
       </c>
       <c r="B17" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57968</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2310,12 +2305,7 @@
         <v>123408381</v>
       </c>
       <c r="B18" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
